--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20221.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -68,6 +68,33 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>YULIET</t>
+  </si>
+  <si>
+    <t>ANETTE JOCELYN</t>
   </si>
 </sst>
 </file>
@@ -559,16 +586,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>92.68000000000001</v>
+      </c>
+      <c r="H2">
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -582,16 +612,19 @@
         <v>45</v>
       </c>
       <c r="D3">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>84.44</v>
+      </c>
+      <c r="H3">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -647,16 +680,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -673,16 +706,16 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>93.33</v>
+        <v>88.89</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -692,7 +725,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -722,6 +755,75 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920282</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920303</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920306</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20221.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MOTA</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>MARIA DEL CARMEN</t>
   </si>
   <si>
@@ -95,6 +101,9 @@
   </si>
   <si>
     <t>ANETTE JOCELYN</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
   </si>
 </sst>
 </file>
@@ -612,19 +621,19 @@
         <v>45</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>84.44</v>
+        <v>86.67</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -706,13 +715,13 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>88.89</v>
+        <v>86.67</v>
       </c>
       <c r="H3">
         <v>7.4</v>
@@ -725,7 +734,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -763,10 +772,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -786,10 +795,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -798,7 +807,7 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -809,10 +818,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -821,6 +830,29 @@
         <v>10</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920308</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20221.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20221.xlsx
@@ -73,37 +73,37 @@
     <t>TERCERO</t>
   </si>
   <si>
+    <t>MOTA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MOTA</t>
-  </si>
-  <si>
     <t>CARRILLO</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
     <t>MARIA DEL CARMEN</t>
   </si>
   <si>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
     <t>YULIET</t>
   </si>
   <si>
     <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
-    <t>ANGEL DIEGO</t>
   </si>
 </sst>
 </file>
@@ -789,7 +789,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920303</v>
+        <v>21330051920308</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
@@ -807,12 +807,12 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920306</v>
+        <v>21330051920303</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
@@ -835,7 +835,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920308</v>
+        <v>21330051920306</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20221.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20221.xlsx
@@ -530,10 +530,10 @@
         <v>45</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>42</v>
@@ -621,10 +621,10 @@
         <v>45</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>39</v>
@@ -712,10 +712,10 @@
         <v>45</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>39</v>
@@ -724,7 +724,7 @@
         <v>86.67</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20221.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -70,6 +70,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
     <t>TERCERO</t>
   </si>
   <si>
@@ -82,6 +85,9 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>ARCADIO</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
@@ -92,6 +98,9 @@
   </si>
   <si>
     <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ANA LILIANA</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
@@ -734,7 +743,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -766,16 +775,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920282</v>
+        <v>21330051920262</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -789,22 +798,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920308</v>
+        <v>21330051920282</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -812,16 +821,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920303</v>
+        <v>21330051920308</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -830,21 +839,21 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920306</v>
+        <v>21330051920303</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -853,6 +862,29 @@
         <v>10</v>
       </c>
       <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920306</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20221.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -70,49 +70,37 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
     <t>HIDALGO</t>
   </si>
   <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
   </si>
   <si>
     <t>ARCADIO</t>
   </si>
   <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MELANI PAOLA</t>
   </si>
   <si>
     <t>ANA LILIANA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
-    <t>YULIET</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
   </si>
 </sst>
 </file>
@@ -698,16 +686,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>92.68000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -724,16 +712,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>86.67</v>
+        <v>88.89</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -743,7 +731,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -775,16 +763,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920262</v>
+        <v>21330051920081</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -804,10 +792,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -821,70 +809,47 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920308</v>
+        <v>21330051920252</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920303</v>
+        <v>21330051920262</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920306</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
     </row>
